--- a/data/trans_orig/P1410-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1410-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de trastornos cardíacos en 2007</t>
+          <t>Población con diagnóstico de trastornos cardíacos en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>85460</t>
+          <t>85759</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>122423</t>
+          <t>123113</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>86002</t>
+          <t>85329</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>125419</t>
+          <t>125420</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>179955</t>
+          <t>181945</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>234905</t>
+          <t>235003</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>909300</t>
+          <t>908610</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>946263</t>
+          <t>945964</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>88,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1189694</t>
+          <t>1189693</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1229111</t>
+          <t>1229784</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2111930</t>
+          <t>2111832</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2166880</t>
+          <t>2164890</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,25%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23040</t>
+          <t>22416</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>44610</t>
+          <t>43997</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12975</t>
+          <t>12966</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31628</t>
+          <t>30967</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>41104</t>
+          <t>39684</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>67893</t>
+          <t>68431</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1648803</t>
+          <t>1649416</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1670373</t>
+          <t>1670997</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1556045</t>
+          <t>1556706</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1574698</t>
+          <t>1574707</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3213193</t>
+          <t>3212655</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3239982</t>
+          <t>3241402</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,79%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8132</t>
+          <t>8355</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24484</t>
+          <t>24625</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7256</t>
+          <t>8320</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10272</t>
+          <t>10294</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28074</t>
+          <t>27532</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>526924</t>
+          <t>526783</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>543276</t>
+          <t>543053</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>469156</t>
+          <t>468092</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>999746</t>
+          <t>1000288</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1017548</t>
+          <t>1017526</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>130747</t>
+          <t>128507</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>174841</t>
+          <t>175060</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>105804</t>
+          <t>105205</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>151020</t>
+          <t>150696</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>246944</t>
+          <t>244433</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>308669</t>
+          <t>310370</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,66%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3101702</t>
+          <t>3101483</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3145796</t>
+          <t>3148036</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3228177</t>
+          <t>3228501</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3273393</t>
+          <t>3273992</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6347072</t>
+          <t>6345371</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6408797</t>
+          <t>6411308</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,33%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de trastornos cardíacos en 2012</t>
+          <t>Población con diagnóstico de trastornos cardíacos en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>78348</t>
+          <t>78648</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>115914</t>
+          <t>115965</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>103037</t>
+          <t>103173</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>145759</t>
+          <t>144647</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>194014</t>
+          <t>188458</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>251250</t>
+          <t>247504</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,71%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>858729</t>
+          <t>858678</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>896295</t>
+          <t>895995</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>88,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1190855</t>
+          <t>1191967</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1233577</t>
+          <t>1233441</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2060007</t>
+          <t>2063753</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2117243</t>
+          <t>2122799</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>91,85%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23465</t>
+          <t>22510</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>45723</t>
+          <t>47195</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15399</t>
+          <t>15076</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>35456</t>
+          <t>36452</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>42789</t>
+          <t>43472</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>75511</t>
+          <t>73489</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1918234</t>
+          <t>1916762</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1940492</t>
+          <t>1941447</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1719136</t>
+          <t>1718140</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1739193</t>
+          <t>1739516</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3643038</t>
+          <t>3645060</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3675760</t>
+          <t>3675077</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,83%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>964</t>
+          <t>981</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9007</t>
+          <t>8208</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3062,7 +3062,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6855</t>
+          <t>7337</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>1976</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11085</t>
+          <t>12251</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>472174</t>
+          <t>472973</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>480217</t>
+          <t>480200</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>451776</t>
+          <t>451294</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>928728</t>
+          <t>927562</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>937796</t>
+          <t>937837</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>110448</t>
+          <t>111617</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>157079</t>
+          <t>156188</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>126911</t>
+          <t>126154</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>171757</t>
+          <t>172797</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>248229</t>
+          <t>248992</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>312091</t>
+          <t>315234</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3262703</t>
+          <t>3263594</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3309334</t>
+          <t>3308165</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3378080</t>
+          <t>3377040</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3422926</t>
+          <t>3423683</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6657528</t>
+          <t>6654385</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6721390</t>
+          <t>6720627</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,43%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de trastornos cardíacos en 2016</t>
+          <t>Población con diagnóstico de trastornos cardíacos en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>46269</t>
+          <t>44437</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>73015</t>
+          <t>73216</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>82793</t>
+          <t>85054</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>125414</t>
+          <t>125619</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>137068</t>
+          <t>136072</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>185288</t>
+          <t>187571</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,72%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>681332</t>
+          <t>681131</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>708078</t>
+          <t>709910</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,32%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>869246</t>
+          <t>869041</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>911867</t>
+          <t>909606</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>87,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1563719</t>
+          <t>1561436</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1611939</t>
+          <t>1612935</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>89,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,22%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>44517</t>
+          <t>46105</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>75650</t>
+          <t>76680</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>32510</t>
+          <t>32423</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>62744</t>
+          <t>61203</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>85818</t>
+          <t>85707</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>128955</t>
+          <t>128908</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2000735</t>
+          <t>1999705</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2031868</t>
+          <t>2030280</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1925556</t>
+          <t>1927097</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1955790</t>
+          <t>1955877</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3935730</t>
+          <t>3935777</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3978867</t>
+          <t>3978978</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4510</t>
+          <t>4029</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19374</t>
+          <t>18398</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5295</t>
+          <t>5020</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18891</t>
+          <t>18544</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12878</t>
+          <t>12346</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30703</t>
+          <t>30777</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>527512</t>
+          <t>528488</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>542376</t>
+          <t>542857</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>530249</t>
+          <t>530596</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>543845</t>
+          <t>544120</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1065324</t>
+          <t>1065250</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1083149</t>
+          <t>1083681</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,87%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>106682</t>
+          <t>106648</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>151192</t>
+          <t>151465</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>134542</t>
+          <t>135225</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>187376</t>
+          <t>186273</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>251939</t>
+          <t>253792</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>320384</t>
+          <t>323747</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,69%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3226426</t>
+          <t>3226153</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3270936</t>
+          <t>3270970</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3344724</t>
+          <t>3345827</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3397558</t>
+          <t>3396875</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6589334</t>
+          <t>6585971</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6657779</t>
+          <t>6655926</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,33%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de trastornos cardíacos en 2023</t>
+          <t>Población con diagnóstico de trastornos cardíacos en 2023 (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>56365</t>
+          <t>56425</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>82312</t>
+          <t>82221</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>79926</t>
+          <t>81194</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>107157</t>
+          <t>106532</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>143507</t>
+          <t>144444</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>181343</t>
+          <t>180428</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,25%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>431630</t>
+          <t>431721</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>457577</t>
+          <t>457517</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,98%</t>
+          <t>84,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>645417</t>
+          <t>646042</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>672648</t>
+          <t>671380</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,76%</t>
+          <t>85,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1085173</t>
+          <t>1086088</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1123009</t>
+          <t>1122072</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>85,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,6%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>55281</t>
+          <t>56972</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>104134</t>
+          <t>104275</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>27665</t>
+          <t>26732</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51060</t>
+          <t>52563</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>91976</t>
+          <t>93212</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>145969</t>
+          <t>144250</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2184154</t>
+          <t>2184013</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2233007</t>
+          <t>2231316</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2183800</t>
+          <t>2182297</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2207195</t>
+          <t>2208128</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4377179</t>
+          <t>4378898</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4431172</t>
+          <t>4429936</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,94%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18418</t>
+          <t>19433</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36821</t>
+          <t>36840</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10566</t>
+          <t>10539</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23551</t>
+          <t>23183</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>32794</t>
+          <t>32508</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>55485</t>
+          <t>54878</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,2%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>609802</t>
+          <t>609783</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>628205</t>
+          <t>627190</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>636752</t>
+          <t>637120</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>649737</t>
+          <t>649764</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,7 +6391,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1251442</t>
+          <t>1252049</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1274133</t>
+          <t>1274419</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,51%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>137889</t>
+          <t>132531</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>204729</t>
+          <t>204945</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>123929</t>
+          <t>120522</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>168952</t>
+          <t>171597</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>279340</t>
+          <t>279049</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>363435</t>
+          <t>361015</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,09%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3244124</t>
+          <t>3243908</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3310964</t>
+          <t>3316322</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6704,7 +6704,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3478785</t>
+          <t>3476140</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3523808</t>
+          <t>3527215</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6733155</t>
+          <t>6735575</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6817250</t>
+          <t>6817541</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,07%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1410-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1410-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>85759</t>
+          <t>86214</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>123113</t>
+          <t>122641</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>85329</t>
+          <t>86439</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>125420</t>
+          <t>126206</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>181945</t>
+          <t>180482</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>235003</t>
+          <t>235775</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,05%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>908610</t>
+          <t>909082</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>945964</t>
+          <t>945509</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1189693</t>
+          <t>1188907</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1229784</t>
+          <t>1228674</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2111832</t>
+          <t>2111060</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2164890</t>
+          <t>2166353</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,31%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22416</t>
+          <t>23260</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>43997</t>
+          <t>44690</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12966</t>
+          <t>13006</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30967</t>
+          <t>30073</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>39684</t>
+          <t>40544</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>68431</t>
+          <t>67512</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1649416</t>
+          <t>1648723</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1670997</t>
+          <t>1670153</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1556706</t>
+          <t>1557600</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1574707</t>
+          <t>1574667</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3212655</t>
+          <t>3213574</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3241402</t>
+          <t>3240542</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,76%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8355</t>
+          <t>8545</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24625</t>
+          <t>23843</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8320</t>
+          <t>8110</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10294</t>
+          <t>10249</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27532</t>
+          <t>27172</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>526783</t>
+          <t>527565</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>543053</t>
+          <t>542863</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>468092</t>
+          <t>468302</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1000288</t>
+          <t>1000648</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1017526</t>
+          <t>1017571</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>128507</t>
+          <t>128162</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>175060</t>
+          <t>176137</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>105205</t>
+          <t>106550</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>150696</t>
+          <t>149062</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>244433</t>
+          <t>246647</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>310370</t>
+          <t>309740</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,65%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3101483</t>
+          <t>3100406</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3148036</t>
+          <t>3148381</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3228501</t>
+          <t>3230135</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3273992</t>
+          <t>3272647</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6345371</t>
+          <t>6346001</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6411308</t>
+          <t>6409094</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,29%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>78648</t>
+          <t>78644</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>115965</t>
+          <t>118548</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2356,7 +2356,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>103173</t>
+          <t>103527</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>144647</t>
+          <t>146181</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>188458</t>
+          <t>190358</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>247504</t>
+          <t>249925</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,81%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>858678</t>
+          <t>856095</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>895995</t>
+          <t>895999</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>87,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1191967</t>
+          <t>1190433</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1233441</t>
+          <t>1233087</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2063753</t>
+          <t>2061332</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2122799</t>
+          <t>2120899</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>89,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,76%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22510</t>
+          <t>22362</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>47195</t>
+          <t>46214</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15076</t>
+          <t>15434</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36452</t>
+          <t>37162</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>43472</t>
+          <t>43569</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>73489</t>
+          <t>74810</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1916762</t>
+          <t>1917743</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1941447</t>
+          <t>1941595</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1718140</t>
+          <t>1717430</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1739516</t>
+          <t>1739158</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3645060</t>
+          <t>3643739</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3675077</t>
+          <t>3674980</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>981</t>
+          <t>979</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8208</t>
+          <t>8032</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3062,7 +3062,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7337</t>
+          <t>6656</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1976</t>
+          <t>1992</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12251</t>
+          <t>11728</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>472973</t>
+          <t>473149</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>480200</t>
+          <t>480202</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>451294</t>
+          <t>451975</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>927562</t>
+          <t>928085</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>937837</t>
+          <t>937821</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>111617</t>
+          <t>111479</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>156188</t>
+          <t>157585</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>126154</t>
+          <t>125697</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>172797</t>
+          <t>173111</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>248992</t>
+          <t>251815</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>315234</t>
+          <t>316202</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,54%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3263594</t>
+          <t>3262197</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3308165</t>
+          <t>3308303</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3377040</t>
+          <t>3376726</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3423683</t>
+          <t>3424140</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6654385</t>
+          <t>6653417</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6720627</t>
+          <t>6717804</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,39%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>44437</t>
+          <t>45273</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>73216</t>
+          <t>72267</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>85054</t>
+          <t>83587</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>125619</t>
+          <t>125678</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>136072</t>
+          <t>137947</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>187571</t>
+          <t>185172</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,59%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>681131</t>
+          <t>682080</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>709910</t>
+          <t>709074</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>869041</t>
+          <t>868982</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>909606</t>
+          <t>911073</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,37%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1561436</t>
+          <t>1563835</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1612935</t>
+          <t>1611060</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,28%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,11%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>46105</t>
+          <t>44553</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>76680</t>
+          <t>76795</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>32423</t>
+          <t>35015</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>61203</t>
+          <t>60916</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>85707</t>
+          <t>86947</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>128908</t>
+          <t>128424</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1999705</t>
+          <t>1999590</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2030280</t>
+          <t>2031832</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1927097</t>
+          <t>1927384</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1955877</t>
+          <t>1953285</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3935777</t>
+          <t>3936261</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3978978</t>
+          <t>3977738</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,86%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4029</t>
+          <t>4249</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18398</t>
+          <t>19235</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5020</t>
+          <t>5287</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18544</t>
+          <t>18872</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12346</t>
+          <t>12088</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30777</t>
+          <t>31159</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,84%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>528488</t>
+          <t>527651</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>542857</t>
+          <t>542637</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>530596</t>
+          <t>530268</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>544120</t>
+          <t>543853</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1065250</t>
+          <t>1064868</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1083681</t>
+          <t>1083939</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,9%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>106648</t>
+          <t>108354</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>151465</t>
+          <t>151800</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>135225</t>
+          <t>134189</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>186273</t>
+          <t>186910</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>253792</t>
+          <t>256022</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>323747</t>
+          <t>323305</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,68%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3226153</t>
+          <t>3225818</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3270970</t>
+          <t>3269264</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3345827</t>
+          <t>3345190</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3396875</t>
+          <t>3397911</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6585971</t>
+          <t>6586413</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6655926</t>
+          <t>6653696</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,29%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>68717</t>
+          <t>73867</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>56425</t>
+          <t>60669</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>82221</t>
+          <t>89128</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>92648</t>
+          <t>100466</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>81194</t>
+          <t>88276</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>106532</t>
+          <t>116114</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>161365</t>
+          <t>174333</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>144444</t>
+          <t>154395</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>180428</t>
+          <t>195139</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>13,96%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>445225</t>
+          <t>503675</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>431721</t>
+          <t>488414</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>457517</t>
+          <t>516873</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>87,21%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>84,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>89,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>659926</t>
+          <t>720243</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>646042</t>
+          <t>704595</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>671380</t>
+          <t>732433</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1105151</t>
+          <t>1223918</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1086088</t>
+          <t>1203112</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1122072</t>
+          <t>1243856</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>86,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>88,96%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>513942</t>
+          <t>577542</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>513942</t>
+          <t>577542</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>513942</t>
+          <t>577542</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>752574</t>
+          <t>820709</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>752574</t>
+          <t>820709</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>752574</t>
+          <t>820709</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1266516</t>
+          <t>1398251</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1266516</t>
+          <t>1398251</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1266516</t>
+          <t>1398251</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>81159</t>
+          <t>85237</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>56972</t>
+          <t>69124</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>104275</t>
+          <t>104401</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>39144</t>
+          <t>45051</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26732</t>
+          <t>35032</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>52563</t>
+          <t>59362</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>120303</t>
+          <t>130288</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>93212</t>
+          <t>109962</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>144250</t>
+          <t>152849</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,48%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2207129</t>
+          <t>2143080</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2184013</t>
+          <t>2123916</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2231316</t>
+          <t>2159193</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2195716</t>
+          <t>2123246</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2182297</t>
+          <t>2108935</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2208128</t>
+          <t>2133265</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4402845</t>
+          <t>4266327</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4378898</t>
+          <t>4243766</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4429936</t>
+          <t>4286653</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,5%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2288288</t>
+          <t>2228317</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2288288</t>
+          <t>2228317</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2288288</t>
+          <t>2228317</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2234860</t>
+          <t>2168297</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2234860</t>
+          <t>2168297</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2234860</t>
+          <t>2168297</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4523148</t>
+          <t>4396615</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4523148</t>
+          <t>4396615</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4523148</t>
+          <t>4396615</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>26508</t>
+          <t>31274</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19433</t>
+          <t>22749</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36840</t>
+          <t>42349</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,17 +6258,17 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>15802</t>
+          <t>17511</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10539</t>
+          <t>11507</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23183</t>
+          <t>25363</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>42311</t>
+          <t>48785</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>32508</t>
+          <t>37701</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>54878</t>
+          <t>62568</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>620115</t>
+          <t>680313</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>609783</t>
+          <t>669238</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>627190</t>
+          <t>688838</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,17 +6371,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>644501</t>
+          <t>716684</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>637120</t>
+          <t>708832</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>649764</t>
+          <t>722688</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1264616</t>
+          <t>1396997</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1252049</t>
+          <t>1383214</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1274419</t>
+          <t>1408081</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,39%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660303</t>
+          <t>734195</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660303</t>
+          <t>734195</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660303</t>
+          <t>734195</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1306927</t>
+          <t>1445782</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1306927</t>
+          <t>1445782</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1306927</t>
+          <t>1445782</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>176383</t>
+          <t>190378</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>132531</t>
+          <t>167754</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>204945</t>
+          <t>217750</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>147595</t>
+          <t>163028</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>120522</t>
+          <t>143583</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>171597</t>
+          <t>183381</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>323978</t>
+          <t>353406</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>279049</t>
+          <t>317233</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>361015</t>
+          <t>384108</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,3%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3272470</t>
+          <t>3327068</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3243908</t>
+          <t>3299696</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3316322</t>
+          <t>3349692</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3500142</t>
+          <t>3560173</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3476140</t>
+          <t>3539820</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3527215</t>
+          <t>3579618</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6772612</t>
+          <t>6887242</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6735575</t>
+          <t>6856540</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6817541</t>
+          <t>6923415</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>95,62%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3448853</t>
+          <t>3517446</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3448853</t>
+          <t>3517446</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3448853</t>
+          <t>3517446</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3647737</t>
+          <t>3723201</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3647737</t>
+          <t>3723201</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3647737</t>
+          <t>3723201</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7096590</t>
+          <t>7240648</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7096590</t>
+          <t>7240648</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7096590</t>
+          <t>7240648</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
